--- a/projects/KE_Kapiti_Eddy_July/data/TLU_equivalents.xlsx
+++ b/projects/KE_Kapiti_Eddy_July/data/TLU_equivalents.xlsx
@@ -5,21 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hawkj\Documents\Github\L-DNDC\Landscape-DNDC\projects\KE_Kapiti_Eddy_July\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\Soil.C.modelling\Kapiti.soil.C\projects\KE_Kapiti_Eddy_July\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDB5605C-8218-4A1B-8FFF-EBDDE681E4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C955B0C-D97E-45DB-B46E-236BA5E3E492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7D6A7CBB-A779-4F14-BBC7-AE4A459C8B60}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,68 +28,110 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Average weight (kg)</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
   <si>
     <t>Buffalo</t>
   </si>
   <si>
+    <t>Sinclair (1977)</t>
+  </si>
+  <si>
     <t>Bush Duiker</t>
   </si>
   <si>
+    <t>Kingdon (1997)</t>
+  </si>
+  <si>
     <t>Bushbuck</t>
   </si>
   <si>
+    <t>Simpson (1974)</t>
+  </si>
+  <si>
     <t>Coke's Hartebeest</t>
   </si>
   <si>
+    <t>Coe et al. (1976)</t>
+  </si>
+  <si>
     <t>Dik-Dik</t>
   </si>
   <si>
+    <t>Hendrichs &amp; Hendrichs (1971)</t>
+  </si>
+  <si>
     <t>Eland</t>
   </si>
   <si>
     <t>Gerenuk</t>
   </si>
   <si>
+    <t>Leuthold (1978)</t>
+  </si>
+  <si>
     <t>Grant's Gazelle</t>
   </si>
   <si>
     <t>Impala</t>
   </si>
   <si>
+    <t>Jarman (1974)</t>
+  </si>
+  <si>
     <t>Lesser Kudu</t>
   </si>
   <si>
+    <t>Leuthold (1979)</t>
+  </si>
+  <si>
     <t>Masai Giraffe</t>
   </si>
   <si>
+    <t>Pellew (1983)</t>
+  </si>
+  <si>
     <t>Reedbuck</t>
   </si>
   <si>
+    <t>Haltenorth &amp; Diller (1980)</t>
+  </si>
+  <si>
     <t>Steinbok</t>
   </si>
   <si>
+    <t>Skinner &amp; Chimimba (2005)</t>
+  </si>
+  <si>
     <t>Thomson's Gazelle</t>
   </si>
   <si>
+    <t>FitzGibbon (1990)</t>
+  </si>
+  <si>
     <t>Wildebeest</t>
   </si>
   <si>
+    <t>Sinclair &amp; Norton-Griffiths (1979)</t>
+  </si>
+  <si>
     <t>Zebra</t>
   </si>
   <si>
-    <t>Species</t>
-  </si>
-  <si>
-    <t>Average weight</t>
+    <t>TLU.equiv</t>
   </si>
 </sst>
 </file>
@@ -491,147 +530,270 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4F1E381-89E0-42F3-9496-4F2987E3A534}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>450</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <f>B2/250</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D17" si="0">B3/250</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1">
+        <v>125</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1">
+        <v>340</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B9" s="1">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
+      <c r="B10" s="1">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>0.17199999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1">
+        <v>750</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="1">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="1">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="1">
+        <v>140</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="1">
+        <v>200</v>
+      </c>
+      <c r="C17" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1</v>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>